--- a/artfynd/A 53977-2023 artfynd.xlsx
+++ b/artfynd/A 53977-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129712233</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129712151</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53977-2023 artfynd.xlsx
+++ b/artfynd/A 53977-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129712233</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>57538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129712151</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>57538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53977-2023 artfynd.xlsx
+++ b/artfynd/A 53977-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129712233</v>
       </c>
       <c r="B2" t="n">
-        <v>57538</v>
+        <v>57541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>129712151</v>
       </c>
       <c r="B3" t="n">
-        <v>57538</v>
+        <v>57541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53977-2023 artfynd.xlsx
+++ b/artfynd/A 53977-2023 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129712151</v>
       </c>
       <c r="B3" t="n">
-        <v>57541</v>
+        <v>57664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53977-2023 artfynd.xlsx
+++ b/artfynd/A 53977-2023 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>129712151</v>
       </c>
       <c r="B3" t="n">
-        <v>57664</v>
+        <v>57665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53977-2023 artfynd.xlsx
+++ b/artfynd/A 53977-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129712233</v>
+        <v>129712151</v>
       </c>
       <c r="B2" t="n">
-        <v>57541</v>
+        <v>57754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,18 +705,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -726,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538153</v>
+        <v>538192</v>
       </c>
       <c r="R2" t="n">
-        <v>6672481</v>
+        <v>6672567</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -772,11 +768,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>02:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hanen spelar, honan dyker upp (honläte) och flyger förbi lågt, hanen följer efter och båda landar en bit bort på hygger (parning?)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129712151</v>
+        <v>129712233</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,14 +824,18 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>parning/parningsceremonier</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538192</v>
+        <v>538153</v>
       </c>
       <c r="R3" t="n">
-        <v>6672567</v>
+        <v>6672481</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,6 +891,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>02:50</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hanen spelar, honan dyker upp (honläte) och flyger förbi lågt, hanen följer efter och båda landar en bit bort på hygger (parning?)</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 53977-2023 artfynd.xlsx
+++ b/artfynd/A 53977-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,8 +929,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>